--- a/KAMCHATKA_ZAPOLNENIE/17_АО_АБС_ЗЭиМ_Автоматизация.xlsx
+++ b/KAMCHATKA_ZAPOLNENIE/17_АО_АБС_ЗЭиМ_Автоматизация.xlsx
@@ -85,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -107,6 +107,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -485,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AE7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -598,7 +601,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Нацрежим ПП 1875 (ограничение): обязательны производитель, страна и ДЕЙСТВУЮЩИЙ номер реестровой записи ПП 719 (для ЕАЭС — евразийский реестр). Приложите выписку из ГИСП и сертификаты. Доставка — до Петропавловска-Камчатского (укажите вес).</t>
+          <t>Графы марка / производитель / страна / № записи частично ПРЕДЗАПОЛНЕНЫ нами по вашему КП и открытым данным — проверьте и исправьте, если не так.</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -632,238 +635,275 @@
       <c r="AD3" s="2" t="n"/>
       <c r="AE3" s="2" t="n"/>
     </row>
-    <row r="4" ht="66" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Нацрежим ПП 1875 (ограничение): обязательны производитель, страна и ДЕЙСТВУЮЩИЙ номер реестровой записи ПП 719 (для ЕАЭС — евразийский реестр). Приложите выписку из ГИСП и сертификаты. Доставка — до Петропавловска-Камчатского (укажите вес).</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n"/>
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="n"/>
+      <c r="T4" s="2" t="n"/>
+      <c r="U4" s="2" t="n"/>
+      <c r="V4" s="2" t="n"/>
+      <c r="W4" s="2" t="n"/>
+      <c r="X4" s="2" t="n"/>
+      <c r="Y4" s="2" t="n"/>
+      <c r="Z4" s="2" t="n"/>
+      <c r="AA4" s="2" t="n"/>
+      <c r="AB4" s="2" t="n"/>
+      <c r="AC4" s="2" t="n"/>
+      <c r="AD4" s="2" t="n"/>
+      <c r="AE4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="66" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Табл./№ ТЗ</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>ГОСТ/ТУ</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Ду, мм</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Проход</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Давление, МПа</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Температура, °С</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Среда</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Материал корпуса</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Климатическое исполнение</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Присоединение</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Приводное устройство: наименование</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Приводное устройство: технические характеристики</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Установочное положение</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>Материал штока, шара, уплотнений</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>Габариты</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>Кол-во</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>Ед.</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr">
+      <c r="U5" s="4" t="inlineStr">
         <is>
           <t>Предлагаемая марка / обозначение</t>
         </is>
       </c>
-      <c r="V4" s="4" t="inlineStr">
+      <c r="V5" s="4" t="inlineStr">
         <is>
           <t>Производитель (завод)</t>
         </is>
       </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="W5" s="4" t="inlineStr">
         <is>
           <t>Страна происхождения</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="X5" s="4" t="inlineStr">
         <is>
           <t>№ реестровой записи (ПП 719) или евразийского реестра</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Y5" s="4" t="inlineStr">
         <is>
           <t>Срок действия записи</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>Соответствие ТЗ: «да» или отличия</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="AA5" s="4" t="inlineStr">
         <is>
           <t>Цена за ед. с НДС, ₽</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr">
+      <c r="AB5" s="4" t="inlineStr">
         <is>
           <t>Сумма с НДС, ₽</t>
         </is>
       </c>
-      <c r="AC4" s="4" t="inlineStr">
+      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>Срок отгрузки</t>
         </is>
       </c>
-      <c r="AD4" s="4" t="inlineStr">
+      <c r="AD5" s="4" t="inlineStr">
         <is>
           <t>Вес ед., кг / габариты</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr">
+      <c r="AE5" s="4" t="inlineStr">
         <is>
           <t>Сертификат / декларация ТР ТС №</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="5" t="n">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>1.6/93</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Электропривод Esbe 95 - 12051900</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>-5...+55</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
         <is>
           <t>Сервопривод ESBE 95 для моторизованных ротационных трехходовых клапанов ESBE Ду 15-150.
 Рабочий диапазон действия регулируется от 30° до 180° при помощи кулачковых дисков. Кулачковые диски также приводят в действие ограничительные выключатели.
@@ -872,70 +912,78 @@
 VRG100*, VRG200*, VRG300*, VRB100*, F, MG, G, BIV, H и HG.</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr"/>
-      <c r="R5" s="6" t="inlineStr"/>
-      <c r="S5" s="5" t="n">
+      <c r="Q6" s="6" t="inlineStr"/>
+      <c r="R6" s="6" t="inlineStr"/>
+      <c r="S6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="T5" s="6" t="inlineStr">
+      <c r="T6" s="6" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="U5" s="7" t="n"/>
-      <c r="V5" s="7" t="n"/>
-      <c r="W5" s="7" t="n"/>
-      <c r="X5" s="7" t="n"/>
-      <c r="Y5" s="7" t="n"/>
-      <c r="Z5" s="7" t="n"/>
-      <c r="AA5" s="8" t="n"/>
-      <c r="AB5" s="9">
-        <f>AA5*S5</f>
+      <c r="U6" s="7" t="n"/>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>АО «АБС ЗЭиМ Автоматизация»</t>
+        </is>
+      </c>
+      <c r="W6" s="8" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X6" s="7" t="n"/>
+      <c r="Y6" s="7" t="n"/>
+      <c r="Z6" s="7" t="n"/>
+      <c r="AA6" s="9" t="n"/>
+      <c r="AB6" s="10">
+        <f>AA6*S6</f>
         <v/>
       </c>
-      <c r="AC5" s="7" t="n"/>
-      <c r="AD5" s="7" t="n"/>
-      <c r="AE5" s="7" t="n"/>
+      <c r="AC6" s="7" t="n"/>
+      <c r="AD6" s="7" t="n"/>
+      <c r="AE6" s="7" t="n"/>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="10" t="inlineStr"/>
-      <c r="B6" s="10" t="inlineStr"/>
-      <c r="C6" s="10" t="inlineStr"/>
-      <c r="D6" s="10" t="inlineStr"/>
-      <c r="E6" s="10" t="inlineStr"/>
-      <c r="F6" s="10" t="inlineStr"/>
-      <c r="G6" s="10" t="inlineStr"/>
-      <c r="H6" s="10" t="inlineStr"/>
-      <c r="I6" s="10" t="inlineStr"/>
-      <c r="J6" s="10" t="inlineStr"/>
-      <c r="K6" s="10" t="inlineStr"/>
-      <c r="L6" s="10" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr"/>
-      <c r="N6" s="10" t="inlineStr"/>
-      <c r="O6" s="10" t="inlineStr"/>
-      <c r="P6" s="10" t="inlineStr"/>
-      <c r="Q6" s="10" t="inlineStr"/>
-      <c r="R6" s="10" t="inlineStr"/>
-      <c r="S6" s="10" t="inlineStr"/>
-      <c r="T6" s="10" t="inlineStr"/>
-      <c r="U6" s="10" t="inlineStr"/>
-      <c r="V6" s="10" t="inlineStr"/>
-      <c r="W6" s="10" t="inlineStr"/>
-      <c r="X6" s="10" t="inlineStr"/>
-      <c r="Y6" s="10" t="inlineStr"/>
-      <c r="Z6" s="10" t="inlineStr"/>
-      <c r="AA6" s="10" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="11" t="inlineStr"/>
+      <c r="B7" s="11" t="inlineStr"/>
+      <c r="C7" s="11" t="inlineStr"/>
+      <c r="D7" s="11" t="inlineStr"/>
+      <c r="E7" s="11" t="inlineStr"/>
+      <c r="F7" s="11" t="inlineStr"/>
+      <c r="G7" s="11" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr"/>
+      <c r="I7" s="11" t="inlineStr"/>
+      <c r="J7" s="11" t="inlineStr"/>
+      <c r="K7" s="11" t="inlineStr"/>
+      <c r="L7" s="11" t="inlineStr"/>
+      <c r="M7" s="11" t="inlineStr"/>
+      <c r="N7" s="11" t="inlineStr"/>
+      <c r="O7" s="11" t="inlineStr"/>
+      <c r="P7" s="11" t="inlineStr"/>
+      <c r="Q7" s="11" t="inlineStr"/>
+      <c r="R7" s="11" t="inlineStr"/>
+      <c r="S7" s="11" t="inlineStr"/>
+      <c r="T7" s="11" t="inlineStr"/>
+      <c r="U7" s="11" t="inlineStr"/>
+      <c r="V7" s="11" t="inlineStr"/>
+      <c r="W7" s="11" t="inlineStr"/>
+      <c r="X7" s="11" t="inlineStr"/>
+      <c r="Y7" s="11" t="inlineStr"/>
+      <c r="Z7" s="11" t="inlineStr"/>
+      <c r="AA7" s="11" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="AB6" s="11">
-        <f>SUM(AB5:AB5)</f>
+      <c r="AB7" s="12">
+        <f>SUM(AB6:AB6)</f>
         <v/>
       </c>
-      <c r="AC6" s="2" t="n"/>
-      <c r="AD6" s="2" t="n"/>
-      <c r="AE6" s="2" t="n"/>
+      <c r="AC7" s="2" t="n"/>
+      <c r="AD7" s="2" t="n"/>
+      <c r="AE7" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
